--- a/utils/chemical-physical-mixed-test.xlsx
+++ b/utils/chemical-physical-mixed-test.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="physical" sheetId="1" state="visible" r:id="rId1"/>
@@ -175,7 +175,6 @@
     </font>
     <font>
       <sz val="10.000000"/>
-      <color indexed="64"/>
       <name val="Times New Roman"/>
     </font>
   </fonts>
@@ -187,7 +186,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="21">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -262,6 +261,21 @@
       <top style="medium">
         <color auto="1"/>
       </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -269,10 +283,23 @@
       <left style="thin">
         <color auto="1"/>
       </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color auto="1"/>
       </top>
       <bottom style="thin">
@@ -284,19 +311,6 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -315,12 +329,8 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <top style="none"/>
+      <bottom style="none"/>
       <diagonal style="none"/>
     </border>
     <border>
@@ -363,6 +373,19 @@
       <diagonal style="none"/>
     </border>
     <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
@@ -399,11 +422,11 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top/>
+      <top style="none"/>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
@@ -465,16 +488,13 @@
     <xf fontId="2" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf fontId="2" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="7" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="2" fillId="0" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="7" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="3" fillId="0" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="2" fillId="0" borderId="7" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -504,86 +524,89 @@
     <xf fontId="3" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf fontId="2" fillId="0" borderId="12" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="10" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="13" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="14" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="15" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf fontId="2" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="10" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="12" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="2" fillId="0" borderId="16" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="17" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="18" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="17" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="2" fillId="0" borderId="17" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="14" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="15" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="16" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="15" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="15" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="15" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="2" fillId="0" borderId="17" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="15" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="3" fillId="0" borderId="17" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="15" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="2" fillId="0" borderId="17" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="15" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf fontId="2" fillId="0" borderId="17" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="19" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="18" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="1" fillId="0" borderId="18" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="0" borderId="20" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="20" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="18" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="18" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="18" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="0" borderId="20" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="20" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="20" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="18" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="0" borderId="20" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="18" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="18" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="0" borderId="20" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="20" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="18" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="20" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="18" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="20" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="18" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1146,171 +1169,168 @@
       <c r="B2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="12"/>
-      <c r="I2" s="13">
-        <v>105</v>
+      <c r="H2" s="11"/>
+      <c r="I2" s="12">
+        <v>315</v>
       </c>
       <c r="J2" s="8">
         <v>14</v>
       </c>
-      <c r="K2" s="14">
+      <c r="K2" s="13">
         <v>2200</v>
       </c>
       <c r="L2" s="8">
         <v>10</v>
       </c>
-      <c r="M2" s="15">
+      <c r="M2" s="14">
         <v>4400</v>
       </c>
     </row>
     <row r="3" ht="42.75">
-      <c r="A3" s="16"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="20" t="s">
+      <c r="A3" s="15"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="21" t="s">
+      <c r="G3" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="21"/>
-      <c r="I3" s="22">
-        <v>105</v>
-      </c>
-      <c r="J3" s="17"/>
-      <c r="K3" s="23"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="24"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="22"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="23"/>
     </row>
     <row r="4" ht="42.75">
-      <c r="A4" s="16"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="20" t="s">
+      <c r="A4" s="15"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="21" t="s">
+      <c r="G4" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="21"/>
-      <c r="I4" s="22">
-        <v>105</v>
-      </c>
-      <c r="J4" s="17"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="24"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="23"/>
     </row>
     <row r="5" ht="185.25">
-      <c r="A5" s="16"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="19"/>
+      <c r="A5" s="15"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="18"/>
       <c r="E5" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="20"/>
-      <c r="G5" s="22" t="s">
+      <c r="F5" s="19"/>
+      <c r="G5" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="22"/>
-      <c r="I5" s="22">
+      <c r="H5" s="27"/>
+      <c r="I5" s="27">
         <v>185</v>
       </c>
-      <c r="J5" s="17"/>
-      <c r="K5" s="23"/>
-      <c r="L5" s="17"/>
-      <c r="M5" s="24"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="23"/>
     </row>
     <row r="6" ht="57">
-      <c r="A6" s="16"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="19"/>
+      <c r="A6" s="15"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="18"/>
       <c r="E6" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="20"/>
-      <c r="G6" s="21" t="s">
+      <c r="F6" s="19"/>
+      <c r="G6" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="21"/>
-      <c r="I6" s="22">
+      <c r="H6" s="20"/>
+      <c r="I6" s="27">
         <v>500</v>
       </c>
-      <c r="J6" s="17"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="24"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="23"/>
     </row>
     <row r="7" ht="42.75">
-      <c r="A7" s="16"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="19"/>
+      <c r="A7" s="15"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="18"/>
       <c r="E7" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="20"/>
-      <c r="G7" s="21" t="s">
+      <c r="F7" s="19"/>
+      <c r="G7" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="21"/>
-      <c r="I7" s="22">
+      <c r="H7" s="20"/>
+      <c r="I7" s="27">
         <v>600</v>
       </c>
-      <c r="J7" s="17"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="17"/>
-      <c r="M7" s="24"/>
+      <c r="J7" s="16"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="16"/>
+      <c r="M7" s="23"/>
     </row>
     <row r="8" ht="42.75">
-      <c r="A8" s="27"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="31" t="s">
+      <c r="A8" s="28"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="32"/>
-      <c r="G8" s="33" t="s">
+      <c r="F8" s="33"/>
+      <c r="G8" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="33"/>
-      <c r="I8" s="34">
+      <c r="H8" s="34"/>
+      <c r="I8" s="35">
         <v>600</v>
       </c>
-      <c r="J8" s="28"/>
-      <c r="K8" s="35"/>
-      <c r="L8" s="28"/>
-      <c r="M8" s="36"/>
+      <c r="J8" s="29"/>
+      <c r="K8" s="36"/>
+      <c r="L8" s="29"/>
+      <c r="M8" s="37"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A2:A8"/>
     <mergeCell ref="B2:B8"/>
     <mergeCell ref="C2:C8"/>
     <mergeCell ref="D2:D8"/>
     <mergeCell ref="E2:E4"/>
+    <mergeCell ref="I2:I4"/>
     <mergeCell ref="J2:J8"/>
     <mergeCell ref="K2:K8"/>
     <mergeCell ref="L2:L8"/>
@@ -1327,239 +1347,239 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" style="37" width="9.140625"/>
-    <col bestFit="1" min="2" max="2" style="37" width="11.9140625"/>
-    <col min="3" max="3" style="37" width="11.9140625"/>
-    <col min="4" max="4" style="37" width="9.140625"/>
-    <col customWidth="1" min="5" max="5" style="37" width="49.57421875"/>
-    <col min="6" max="6" style="37" width="9.140625"/>
-    <col customWidth="1" min="7" max="7" style="37" width="19.8515625"/>
-    <col min="8" max="13" style="37" width="9.140625"/>
+    <col min="1" max="1" style="38" width="9.140625"/>
+    <col bestFit="1" min="2" max="2" style="38" width="11.9140625"/>
+    <col min="3" max="3" style="38" width="11.9140625"/>
+    <col min="4" max="4" style="38" width="9.140625"/>
+    <col customWidth="1" min="5" max="5" style="38" width="49.57421875"/>
+    <col min="6" max="6" style="38" width="9.140625"/>
+    <col customWidth="1" min="7" max="7" style="38" width="19.8515625"/>
+    <col min="8" max="13" style="38" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" ht="71.25">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38" t="s">
+      <c r="C1" s="39"/>
+      <c r="D1" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="39" t="s">
+      <c r="E1" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="39" t="s">
+      <c r="F1" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="38" t="s">
+      <c r="G1" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="38" t="s">
+      <c r="H1" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="40" t="s">
+      <c r="I1" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="39" t="s">
+      <c r="J1" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="39" t="s">
+      <c r="K1" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="39" t="s">
+      <c r="L1" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="39" t="s">
+      <c r="M1" s="40" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" ht="24">
-      <c r="A2" s="41">
+      <c r="A2" s="42">
         <v>48</v>
       </c>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="41" t="s">
+      <c r="C2" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="41" t="s">
+      <c r="D2" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="42" t="s">
+      <c r="E2" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="42"/>
-      <c r="G2" s="43" t="s">
+      <c r="F2" s="43"/>
+      <c r="G2" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="42" t="s">
+      <c r="H2" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="44">
+      <c r="I2" s="45">
         <v>900</v>
       </c>
-      <c r="J2" s="45">
+      <c r="J2" s="46">
         <v>14</v>
       </c>
-      <c r="K2" s="41">
+      <c r="K2" s="42">
         <v>1800</v>
       </c>
-      <c r="L2" s="45">
+      <c r="L2" s="46">
         <v>6</v>
       </c>
-      <c r="M2" s="46">
+      <c r="M2" s="47">
         <v>3600</v>
       </c>
     </row>
     <row r="3" ht="14.25">
-      <c r="A3" s="41"/>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="42" t="s">
+      <c r="A3" s="42"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="42"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="44">
+      <c r="F3" s="43"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="45">
         <v>0</v>
       </c>
-      <c r="J3" s="48">
+      <c r="J3" s="46">
         <v>14</v>
       </c>
-      <c r="K3" s="41"/>
-      <c r="L3" s="48">
+      <c r="K3" s="42"/>
+      <c r="L3" s="46">
         <v>6</v>
       </c>
-      <c r="M3" s="46"/>
+      <c r="M3" s="47"/>
     </row>
     <row r="4" ht="24">
-      <c r="A4" s="41"/>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="42" t="s">
+      <c r="A4" s="42"/>
+      <c r="B4" s="42"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="42"/>
-      <c r="G4" s="43" t="s">
+      <c r="F4" s="43"/>
+      <c r="G4" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="42" t="s">
+      <c r="H4" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="I4" s="44">
+      <c r="I4" s="45">
         <v>300</v>
       </c>
-      <c r="J4" s="48">
+      <c r="J4" s="46">
         <v>14</v>
       </c>
-      <c r="K4" s="41"/>
-      <c r="L4" s="48">
+      <c r="K4" s="42"/>
+      <c r="L4" s="46">
         <v>6</v>
       </c>
-      <c r="M4" s="46"/>
+      <c r="M4" s="47"/>
     </row>
     <row r="5" ht="24">
-      <c r="A5" s="41"/>
-      <c r="B5" s="41"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="42" t="s">
+      <c r="A5" s="42"/>
+      <c r="B5" s="42"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="42"/>
-      <c r="G5" s="43" t="s">
+      <c r="F5" s="43"/>
+      <c r="G5" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="H5" s="42" t="s">
+      <c r="H5" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="I5" s="44">
+      <c r="I5" s="45">
         <v>300</v>
       </c>
-      <c r="J5" s="48">
+      <c r="J5" s="46">
         <v>14</v>
       </c>
-      <c r="K5" s="41"/>
-      <c r="L5" s="48">
+      <c r="K5" s="42"/>
+      <c r="L5" s="46">
         <v>6</v>
       </c>
-      <c r="M5" s="46"/>
+      <c r="M5" s="47"/>
     </row>
     <row r="6" ht="24">
-      <c r="A6" s="41"/>
-      <c r="B6" s="41"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="41"/>
-      <c r="E6" s="42" t="s">
+      <c r="A6" s="42"/>
+      <c r="B6" s="42"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="42"/>
-      <c r="G6" s="43" t="s">
+      <c r="F6" s="43"/>
+      <c r="G6" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="H6" s="42" t="s">
+      <c r="H6" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="I6" s="44">
+      <c r="I6" s="45">
         <v>300</v>
       </c>
-      <c r="J6" s="48">
+      <c r="J6" s="46">
         <v>14</v>
       </c>
-      <c r="K6" s="41"/>
-      <c r="L6" s="48">
+      <c r="K6" s="42"/>
+      <c r="L6" s="46">
         <v>6</v>
       </c>
-      <c r="M6" s="46"/>
+      <c r="M6" s="47"/>
     </row>
     <row r="7" ht="14.25">
-      <c r="A7" s="37"/>
-      <c r="B7" s="37"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="37"/>
-      <c r="J7" s="37"/>
-      <c r="K7" s="37"/>
-      <c r="L7" s="37"/>
+      <c r="A7" s="38"/>
+      <c r="B7" s="38"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="38"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
+      <c r="L7" s="38"/>
     </row>
     <row r="8" ht="14.25">
-      <c r="A8" s="37"/>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="37"/>
-      <c r="J8" s="37"/>
-      <c r="K8" s="37"/>
-      <c r="L8" s="37"/>
+      <c r="A8" s="38"/>
+      <c r="B8" s="38"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="38"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="L8" s="38"/>
     </row>
     <row r="9" ht="14.25">
-      <c r="A9" s="37"/>
-      <c r="B9" s="37"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="37"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="37"/>
-      <c r="J9" s="37"/>
-      <c r="K9" s="37"/>
-      <c r="L9" s="37"/>
+      <c r="A9" s="38"/>
+      <c r="B9" s="38"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="38"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
+      <c r="L9" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="6">
